--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0137.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0137.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Phù, Voidmatter... Ta ước gì có thể quét sạch thứ này khỏi Solaris mãi mãi.</t>
+          <t>Phù, Voidmatter... Tao ước gì có thể quét sạch thứ này khỏi Solaris mãi mãi.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Khi tiếng bip kéo dài thành một tiếng rít chói tai, ta cứ ngỡ thế là xong. Rồi ta cảm nhận được một cú đẩy mạnh vào lưng.</t>
+          <t>Khi tiếng bip kéo dài thành một tiếng rít chói tai, tao cứ ngỡ thế là xong. Rồi tao cảm nhận được một cú đẩy mạnh vào lưng.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ta ngã sấp mặt xuống đất. Nhưng may mà thoát chết.</t>
+          <t>Tao ngã sấp mặt xuống đất. Nhưng may mà thoát chết.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Ta cố lật người lại để nhìn Nahum lần cuối... Giây tiếp theo, cậu ấy đã bị cơn bão cuốn đi.</t>
+          <t>Tao cố lật người lại để nhìn Nahum lần cuối... Giây tiếp theo, cậu ấy đã bị cơn bão cuốn đi.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tỉnh dậy thì ta đã nằm trên giường bệnh ở trạm xá rồi...</t>
+          <t>Tỉnh dậy thì tao đã nằm trên giường bệnh ở trạm xá rồi...</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Sắp tới nơi rồi, chỗ mà ta nghe thấy giọng Nahum... Nhưng thật lòng, giờ ta hơi sợ rồi.</t>
+          <t>Sắp tới nơi rồi, chỗ mà tao nghe thấy giọng Nahum... Nhưng thật lòng, giờ tao hơi sợ rồi.</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Ngày mà Roya giải cứu ta, ta cảm nhận được hơi ấm từ Reactor Drive—một thứ ấm áp mà ta chưa từng biết đến.</t>
+          <t>Ngày mà Roya giải cứu tao, tao cảm nhận được hơi ấm từ Reactor Drive—một thứ ấm áp mà tao chưa từng biết đến.</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Ta cảm ơn sự hỗ trợ kiên định của ngươi, đồng đội Rover.</t>
+          <t>Ta cảm ơn sự hỗ trợ kiên định của ngươi, đồng đội Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Dumdum! Cậu ở trong này hả?</t>
+          <t>Dumdum! Mày ở trong này hả?</t>
         </is>
       </c>
     </row>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Hừm, chính bọn ta hạ gục lũ quái vật đó, thế mà giờ thằng này lại muốn giành hết công về mình!</t>
+          <t>Hừm, chính bọn tao hạ gục lũ quái vật đó, thế mà giờ thằng này lại muốn giành hết công về mình!</t>
         </is>
       </c>
     </row>
